--- a/examples/fee_ledger.xlsx
+++ b/examples/fee_ledger.xlsx
@@ -59,7 +59,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="835">
   <si>
-    <t xml:space="preserve">Summary — all formulas</t>
+    <t xml:space="preserve">Summary  -  all formulas</t>
   </si>
   <si>
     <t xml:space="preserve">Receipts</t>
@@ -74,49 +74,49 @@
     <t xml:space="preserve">Money out (refunds / outflows)</t>
   </si>
   <si>
-    <t xml:space="preserve">Money in — AUT-2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Money in — JAN-2026</t>
+    <t xml:space="preserve">Money in  -  AUT-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money in  -  JAN-2026</t>
   </si>
   <si>
     <t xml:space="preserve">Allocation by tier (all terms)</t>
   </si>
   <si>
-    <t xml:space="preserve">M — manual override  [lines]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M — manual override  [£ in]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A — reference or verified payer alias  [lines]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A — reference or verified payer alias  [£ in]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B — unique surname in memo  [lines]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B — unique surname in memo  [£ in]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C — fuzzy / first name (review)  [lines]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C — fuzzy / first name (review)  [£ in]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D — nothing usable or ambiguous (review)  [lines]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D — nothing usable or ambiguous (review)  [£ in]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X — reference contradicts memo (review)  [lines]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X — reference contradicts memo (review)  [£ in]</t>
+    <t xml:space="preserve">M  -  manual override  [lines]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M  -  manual override  [£ in]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A  -  reference or verified payer alias  [lines]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A  -  reference or verified payer alias  [£ in]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B  -  unique surname in memo  [lines]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B  -  unique surname in memo  [£ in]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C  -  fuzzy / first name (review)  [lines]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C  -  fuzzy / first name (review)  [£ in]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D  -  nothing usable or ambiguous (review)  [lines]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D  -  nothing usable or ambiguous (review)  [£ in]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X  -  reference contradicts memo (review)  [lines]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X  -  reference contradicts memo (review)  [£ in]</t>
   </si>
   <si>
     <t xml:space="preserve">Lines allocated automatically</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">Lines in Review queue</t>
   </si>
   <si>
-    <t xml:space="preserve">Position — JAN-2026</t>
+    <t xml:space="preserve">Position  -  JAN-2026</t>
   </si>
   <si>
     <t xml:space="preserve">Expected income (rules)</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">Outstanding is overstated by whatever sits in Review and by any 2026 money tagged to AUT-2025. The AUT-2025 register is not loaded, so autumn has no position yet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fee ledger — how it works</t>
+    <t xml:space="preserve">Fee ledger  -  how it works</t>
   </si>
   <si>
     <t xml:space="preserve">Built from the pupil roster and the bank export. Health, guardian-contact and free-text pupil columns were deliberately not carried over.</t>
@@ -182,22 +182,22 @@
     <t xml:space="preserve">Where to look</t>
   </si>
   <si>
-    <t xml:space="preserve">Position — the answer sheet. One row per family: what they owe, what came in, every receipt reference, whether it is settled. Colour-coded. Start here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review — the only sheet that needs you. Receipts the engine would not allocate, with candidates and a reason. Decide, type the family ID into Receipts column F, re-run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipts — every bank line and what the engine did with it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Children / Families — the roster, and the fee each child should be charged. Difference and Check compare that with what the roster actually invoiced.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rates / Terms — the fee rules and the session counts. Change a number here and everything recalculates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary — headline figures.</t>
+    <t xml:space="preserve">Position  -  the answer sheet. One row per family: what they owe, what came in, every receipt reference, whether it is settled. Colour-coded. Start here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review  -  the only sheet that needs you. Receipts the engine would not allocate, with candidates and a reason. Decide, type the family ID into Receipts column F, re-run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipts  -  every bank line and what the engine did with it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Children / Families  -  the roster, and the fee each child should be charged. Difference and Check compare that with what the roster actually invoiced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rates / Terms  -  the fee rules and the session counts. Change a number here and everything recalculates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary  -  headline figures.</t>
   </si>
   <si>
     <t xml:space="preserve">Colour key</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">Ranked evidence, first hit wins: your manual override; then the invoice reference, or a payer name already seen with a verified reference; then a unique surname in the memo; then fuzzy evidence such as a truncated surname or a child's first name. The first three allocate automatically, the rest go to Review. If the reference and the payer name disagree, nothing is allocated and the line is flagged.</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumptions — confirm these with the office</t>
+    <t xml:space="preserve">Assumptions  -  confirm these with the office</t>
   </si>
   <si>
     <t xml:space="preserve">Rates come from the January price list: £195 / £345 / £460 / £571 per 10 sessions for 1-4 siblings on Saturdays, £160 per child for Wednesdays, £25 registration, £25 supplies.</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">What the roster got wrong</t>
   </si>
   <si>
-    <t xml:space="preserve">Invoice numbers shared by unrelated families: 2026-008 — so the invoice number cannot be the family key, hence FAM-nnn.</t>
+    <t xml:space="preserve">Invoice numbers shared by unrelated families: 2026-008  -  so the invoice number cannot be the family key, hence FAM-nnn.</t>
   </si>
   <si>
     <t xml:space="preserve">1 enrolled children have no invoice number and no fee. Two of them have payment notes, so money may have arrived with nothing to match it to.</t>
@@ -242,16 +242,16 @@
     <t xml:space="preserve">1 discounts were stored as negative numbers in the supplies column; they are a proper Discount column here. Invoice numbers out of sequence: .</t>
   </si>
   <si>
-    <t xml:space="preserve">One invoice charges £18 supplies instead of £25 — the only invoice the fee rules cannot reproduce.</t>
+    <t xml:space="preserve">One invoice charges £18 supplies instead of £25  -  the only invoice the fee rules cannot reproduce.</t>
   </si>
   <si>
     <t xml:space="preserve">To re-run</t>
   </si>
   <si>
-    <t xml:space="preserve">Replace the bank export, run build_ledger.py then reconcile.py. Copy column F of Receipts and the alias column of Families first — manual decisions live in the workbook, not in the scripts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fee rules — inputs (blue). Source: charity price list, January 2026 (photo supplied by user).</t>
+    <t xml:space="preserve">Replace the bank export, run build_ledger.py then reconcile.py. Copy column F of Receipts and the alias column of Families first  -  manual decisions live in the workbook, not in the scripts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fee rules  -  inputs (blue). Source: charity price list, January 2026 (photo supplied by user).</t>
   </si>
   <si>
     <t xml:space="preserve">Item</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">Source / note</t>
   </si>
   <si>
-    <t xml:space="preserve">Saturday school — 1 child</t>
+    <t xml:space="preserve">Saturday school  -  1 child</t>
   </si>
   <si>
     <t xml:space="preserve">per family per session</t>
@@ -275,25 +275,25 @@
     <t xml:space="preserve">£195 per 10 sessions</t>
   </si>
   <si>
-    <t xml:space="preserve">Saturday school — 2 siblings</t>
+    <t xml:space="preserve">Saturday school  -  2 siblings</t>
   </si>
   <si>
     <t xml:space="preserve">£345 per 10 sessions</t>
   </si>
   <si>
-    <t xml:space="preserve">Saturday school — 3 siblings</t>
+    <t xml:space="preserve">Saturday school  -  3 siblings</t>
   </si>
   <si>
     <t xml:space="preserve">£460 per 10 sessions</t>
   </si>
   <si>
-    <t xml:space="preserve">Saturday school — 4 siblings</t>
+    <t xml:space="preserve">Saturday school  -  4 siblings</t>
   </si>
   <si>
     <t xml:space="preserve">£571 per 10 sessions</t>
   </si>
   <si>
-    <t xml:space="preserve">Wednesday class — per child</t>
+    <t xml:space="preserve">Wednesday class  -  per child</t>
   </si>
   <si>
     <t xml:space="preserve">per child per session</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">per child, one-off at first registration</t>
   </si>
   <si>
-    <t xml:space="preserve">Price list says per family for Wednesday — treated per child here (one Wednesday child only)</t>
+    <t xml:space="preserve">Price list says per family for Wednesday  -  treated per child here (one Wednesday child only)</t>
   </si>
   <si>
     <t xml:space="preserve">Supplies / annual membership</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">Price list</t>
   </si>
   <si>
-    <t xml:space="preserve">Trial — Saturday, 1 child</t>
+    <t xml:space="preserve">Trial  -  Saturday, 1 child</t>
   </si>
   <si>
     <t xml:space="preserve">information only, not used in formulas</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">£34.50 / £46 / £57 for 2 / 3 / 4 siblings</t>
   </si>
   <si>
-    <t xml:space="preserve">Trial — Wednesday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoicing terms — inputs (blue). Add a row per new term; the register for each term goes in Invoices.</t>
+    <t xml:space="preserve">Trial  -  Wednesday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoicing terms  -  inputs (blue). Add a row per new term; the register for each term goes in Invoices.</t>
   </si>
   <si>
     <t xml:space="preserve">Term ID</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">AUT-2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Autumn 2025 (Sep–Dec)</t>
+    <t xml:space="preserve">Autumn 2025 (Sep-Dec)</t>
   </si>
   <si>
     <t xml:space="preserve">2025-5xx / 2025-6xx</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">No</t>
   </si>
   <si>
-    <t xml:space="preserve">Sessions inferred from receipts (£214.50 = 11 × £19.50). Invoice register not supplied — add it to allocate autumn receipts.</t>
+    <t xml:space="preserve">Sessions inferred from receipts (£214.50 = 11 × £19.50). Invoice register not supplied  -  add it to allocate autumn receipts.</t>
   </si>
   <si>
     <t xml:space="preserve">JAN-2026</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">21 = £409.50 ÷ £19.50. Wednesday 20 = £320 ÷ £16 (single club invoice). Confirm both with the office.</t>
   </si>
   <si>
-    <t xml:space="preserve">Families — stable key. One family can have several invoice numbers over time; the family ID never changes.</t>
+    <t xml:space="preserve">Families  -  stable key. One family can have several invoice numbers over time; the family ID never changes.</t>
   </si>
   <si>
     <t xml:space="preserve">Family ID</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">GENEVIEVE BELHADJ</t>
   </si>
   <si>
-    <t xml:space="preserve">invoice number shared with another family — 2026-008</t>
+    <t xml:space="preserve">invoice number shared with another family  -  2026-008</t>
   </si>
   <si>
     <t xml:space="preserve">FAM-009</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">2026-051</t>
   </si>
   <si>
-    <t xml:space="preserve">Children — facts per child (blue) drive the expected fee (black). 'Check' must be OK; anything else is an invoice that does not follow the rules.</t>
+    <t xml:space="preserve">Children  -  facts per child (blue) drive the expected fee (black). 'Check' must be OK; anything else is an invoice that does not follow the rules.</t>
   </si>
   <si>
     <t xml:space="preserve">Child ID</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">CH-094</t>
   </si>
   <si>
-    <t xml:space="preserve">Receipts — one row per bank line. Blue = from the bank file. Yellow = your decision. Everything else is written by the engine.</t>
+    <t xml:space="preserve">Receipts  -  one row per bank line. Blue = from the bank file. Yellow = your decision. Everything else is written by the engine.</t>
   </si>
   <si>
     <t xml:space="preserve">Date</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">FAM-048, FAM-049</t>
   </si>
   <si>
-    <t xml:space="preserve">reference 2026-039 points to FAM-049 but the memo names FAM-048 — parent may have typed the wrong invoice number</t>
+    <t xml:space="preserve">reference 2026-039 points to FAM-049 but the memo names FAM-048  -  parent may have typed the wrong invoice number</t>
   </si>
   <si>
     <t xml:space="preserve">MARGIT RASMUSSEN       	2026-039	BGC	</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">2025-608</t>
   </si>
   <si>
-    <t xml:space="preserve">surname DUPLANTIER (prior-term reference 2025-608 — family identified, invoice not loaded)</t>
+    <t xml:space="preserve">surname DUPLANTIER (prior-term reference 2025-608  -  family identified, invoice not loaded)</t>
   </si>
   <si>
     <t xml:space="preserve">JAN-2026 amount</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">2025-508</t>
   </si>
   <si>
-    <t xml:space="preserve">surname OKONKWO (prior-term reference 2025-508 — family identified, invoice not loaded)</t>
+    <t xml:space="preserve">surname OKONKWO (prior-term reference 2025-508  -  family identified, invoice not loaded)</t>
   </si>
   <si>
     <t xml:space="preserve">NILS OKONKWO           	2025-508	BGC	</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">2025-611</t>
   </si>
   <si>
-    <t xml:space="preserve">payer name previously seen with a verified reference for this family (prior-term reference 2025-611 — family identified, invoice not loaded)</t>
+    <t xml:space="preserve">payer name previously seen with a verified reference for this family (prior-term reference 2025-611  -  family identified, invoice not loaded)</t>
   </si>
   <si>
     <t xml:space="preserve">GENEVIEVE KILBRIDE     	2025-611	BGC	</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">2025-578</t>
   </si>
   <si>
-    <t xml:space="preserve">surname VILLALOBOS (prior-term reference 2025-578 — family identified, invoice not loaded)</t>
+    <t xml:space="preserve">surname VILLALOBOS (prior-term reference 2025-578  -  family identified, invoice not loaded)</t>
   </si>
   <si>
     <t xml:space="preserve">BETTINA VILLALOBOS     	2025-578	BGC	</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">2025-641</t>
   </si>
   <si>
-    <t xml:space="preserve">'PELL' starts PELLETIER, surname NAKASHIMA (prior-term reference 2025-641 — family identified, invoice not loaded)</t>
+    <t xml:space="preserve">'PELL' starts PELLETIER, surname NAKASHIMA (prior-term reference 2025-641  -  family identified, invoice not loaded)</t>
   </si>
   <si>
     <t xml:space="preserve">ROSALIND NAKASHIMA-PELL	2025-641	BGC	</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">FAM-032, FAM-033</t>
   </si>
   <si>
-    <t xml:space="preserve">reference 2026-024 points to FAM-033 but the memo names FAM-032 — parent may have typed the wrong invoice number</t>
+    <t xml:space="preserve">reference 2026-024 points to FAM-033 but the memo names FAM-032  -  parent may have typed the wrong invoice number</t>
   </si>
   <si>
     <t xml:space="preserve">GENEVIEVE HOLLINGWORTH 	2026-024	BGC	</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">2025-574</t>
   </si>
   <si>
-    <t xml:space="preserve">surname ZIMMERLI (prior-term reference 2025-574 — family identified, invoice not loaded)</t>
+    <t xml:space="preserve">surname ZIMMERLI (prior-term reference 2025-574  -  family identified, invoice not loaded)</t>
   </si>
   <si>
     <t xml:space="preserve">ZORA ZIMMERLI          	2025-574	BGC	</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">2025-503</t>
   </si>
   <si>
-    <t xml:space="preserve">surname FERREIRO (prior-term reference 2025-503 — family identified, invoice not loaded)</t>
+    <t xml:space="preserve">surname FERREIRO (prior-term reference 2025-503  -  family identified, invoice not loaded)</t>
   </si>
   <si>
     <t xml:space="preserve">CAMILLE FERREIRO       	2025-503	BGC	</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">JEROME PERREAULT</t>
   </si>
   <si>
-    <t xml:space="preserve">surname PERREAULT (prior-term reference 2025-641 — family identified, invoice not loaded)</t>
+    <t xml:space="preserve">surname PERREAULT (prior-term reference 2025-641  -  family identified, invoice not loaded)</t>
   </si>
   <si>
     <t xml:space="preserve">JEROME PERREAULT       	2025-641	BGC	</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">FAM-008, FAM-009, FAM-042</t>
   </si>
   <si>
-    <t xml:space="preserve">reference 2026-003 points to FAM-042 but the memo names FAM-008, FAM-009 — parent may have typed the wrong invoice number</t>
+    <t xml:space="preserve">reference 2026-003 points to FAM-042 but the memo names FAM-008, FAM-009  -  parent may have typed the wrong invoice number</t>
   </si>
   <si>
     <t xml:space="preserve">MARGIT BELHADJ-TREVELYA	2026-003	BGC	</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">C</t>
   </si>
   <si>
-    <t xml:space="preserve">surname CHIDOZIE — chosen over FAM-016 because only this family is billed this term</t>
+    <t xml:space="preserve">surname CHIDOZIE  -  chosen over FAM-016 because only this family is billed this term</t>
   </si>
   <si>
     <t xml:space="preserve">TOVE CHIDOZIE          	CHIDOZIE FRENCH SCHOO	BGC	</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">INGRID BAPTISTE        	Baptiste	BGC	</t>
   </si>
   <si>
-    <t xml:space="preserve">Review queue — receipts the engine would not allocate. Decide, then type the family ID into Receipts column M (row shown) and re-run.</t>
+    <t xml:space="preserve">Review queue  -  receipts the engine would not allocate. Decide, then type the family ID into Receipts column M (row shown) and re-run.</t>
   </si>
   <si>
     <t xml:space="preserve">Row in Receipts</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">FAM-048 RASMUSSEN, FAM-049 ROCHETEAU</t>
   </si>
   <si>
-    <t xml:space="preserve">Position — JAN-2026. One row per family. Green = settled. Red = owing. Amber = check the last two columns before chasing.</t>
+    <t xml:space="preserve">Position  -  JAN-2026. One row per family. Green = settled. Red = owing. Amber = check the last two columns before chasing.</t>
   </si>
   <si>
     <t xml:space="preserve">Report date</t>

--- a/examples/fee_ledger.xlsx
+++ b/examples/fee_ledger.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Position'!$A$4:$M$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Families'!$A$3:$H$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Children'!$A$3:$V$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Receipts'!$A$3:$N$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Receipts'!$A$3:$O$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Review'!$A$3:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="B2" s="24" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="4">
@@ -15780,7 +15780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15792,11 +15792,12 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15854,25 +15855,30 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
+          <t>Family (engine)</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
           <t>Candidates</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Amount check</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Full memo</t>
         </is>
@@ -15930,7 +15936,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N4" s="34" t="inlineStr">
+      <c r="N4" s="34" t="inlineStr"/>
+      <c r="O4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ZORA VANTERPOOL        	Halima	BGC	</t>
         </is>
@@ -15988,7 +15995,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N5" s="34" t="inlineStr">
+      <c r="N5" s="34" t="inlineStr"/>
+      <c r="O5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">VERA FALZON            	2026018	BGC	</t>
         </is>
@@ -16042,7 +16050,8 @@
         </is>
       </c>
       <c r="M6" s="51" t="inlineStr"/>
-      <c r="N6" s="49" t="inlineStr">
+      <c r="N6" s="49" t="inlineStr"/>
+      <c r="O6" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">MARGIT RASMUSSEN       	2026-039	BGC	</t>
         </is>
@@ -16100,7 +16109,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N7" s="34" t="inlineStr">
+      <c r="N7" s="34" t="inlineStr"/>
+      <c r="O7" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">INGRID ERIKSEN         	ERIKSE2026-017	BGC	</t>
         </is>
@@ -16158,7 +16168,8 @@
           <t>unusual (expected £774.50)</t>
         </is>
       </c>
-      <c r="N8" s="34" t="inlineStr">
+      <c r="N8" s="34" t="inlineStr"/>
+      <c r="O8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">GENEVIEVE BELHADJ      	2026-008	BGC	</t>
         </is>
@@ -16216,7 +16227,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N9" s="34" t="inlineStr">
+      <c r="N9" s="34" t="inlineStr"/>
+      <c r="O9" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">MARGIT GAILLARD        	Esben	BGC	</t>
         </is>
@@ -16276,6 +16288,11 @@
       </c>
       <c r="N10" s="34" t="inlineStr">
         <is>
+          <t>bank truncated the reference field</t>
+        </is>
+      </c>
+      <c r="O10" s="34" t="inlineStr">
+        <is>
           <t xml:space="preserve">LUDOVIC ASHWORTH       	ASHWORTH FRENCH SCHOO	BGC	</t>
         </is>
       </c>
@@ -16332,7 +16349,8 @@
           <t>JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N11" s="34" t="inlineStr">
+      <c r="N11" s="34" t="inlineStr"/>
+      <c r="O11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">KATRIN DUPLANTIER      	2025-608	BGC	</t>
         </is>
@@ -16390,7 +16408,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N12" s="34" t="inlineStr">
+      <c r="N12" s="34" t="inlineStr"/>
+      <c r="O12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">GENEVIEVE MAALOUF      	MAALOU2026-030	BGC	</t>
         </is>
@@ -16448,7 +16467,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N13" s="34" t="inlineStr">
+      <c r="N13" s="34" t="inlineStr"/>
+      <c r="O13" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ELODIE HASANOVIC       	060	BGC	</t>
         </is>
@@ -16506,7 +16526,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N14" s="34" t="inlineStr">
+      <c r="N14" s="34" t="inlineStr"/>
+      <c r="O14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">CAMILLE SIGURDSSON     	2026041	BGC	</t>
         </is>
@@ -16564,7 +16585,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N15" s="34" t="inlineStr">
+      <c r="N15" s="34" t="inlineStr"/>
+      <c r="O15" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">BETTINA DELACROIX      	2026-015	BGC	</t>
         </is>
@@ -16624,6 +16646,11 @@
       </c>
       <c r="N16" s="34" t="inlineStr">
         <is>
+          <t>prior-term ref but 2026-term amount and date  -  parent may have reused old reference</t>
+        </is>
+      </c>
+      <c r="O16" s="34" t="inlineStr">
+        <is>
           <t xml:space="preserve">NILS OKONKWO           	2025-508	BGC	</t>
         </is>
       </c>
@@ -16680,7 +16707,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N17" s="34" t="inlineStr">
+      <c r="N17" s="34" t="inlineStr"/>
+      <c r="O17" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">NILS DZIEDZIC          	2026057	BGC	</t>
         </is>
@@ -16734,7 +16762,8 @@
         </is>
       </c>
       <c r="M18" s="39" t="inlineStr"/>
-      <c r="N18" s="34" t="inlineStr">
+      <c r="N18" s="34" t="inlineStr"/>
+      <c r="O18" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">GENEVIEVE KILBRIDE     	2025-611	BGC	</t>
         </is>
@@ -16792,7 +16821,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N19" s="34" t="inlineStr">
+      <c r="N19" s="34" t="inlineStr"/>
+      <c r="O19" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">MARGIT RASMUSSEN       	Rasmussen	BGC	</t>
         </is>
@@ -16852,6 +16882,11 @@
       </c>
       <c r="N20" s="34" t="inlineStr">
         <is>
+          <t>prior-term ref but 2026-term amount and date  -  parent may have reused old reference</t>
+        </is>
+      </c>
+      <c r="O20" s="34" t="inlineStr">
+        <is>
           <t xml:space="preserve">BETTINA VILLALOBOS     	2025-578	BGC	</t>
         </is>
       </c>
@@ -16908,7 +16943,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N21" s="34" t="inlineStr">
+      <c r="N21" s="34" t="inlineStr"/>
+      <c r="O21" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">INGRID ERIKSEN         	Eriksen 2nd	BGC	</t>
         </is>
@@ -16966,7 +17002,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N22" s="34" t="inlineStr">
+      <c r="N22" s="34" t="inlineStr"/>
+      <c r="O22" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">KATRIN NAKASHIMA       	2026-032	BGC	</t>
         </is>
@@ -17024,7 +17061,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N23" s="34" t="inlineStr">
+      <c r="N23" s="34" t="inlineStr"/>
+      <c r="O23" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">GENEVIEVE MAALOUF      	2nd payment	BGC	</t>
         </is>
@@ -17082,7 +17120,8 @@
           <t>half of expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N24" s="34" t="inlineStr">
+      <c r="N24" s="34" t="inlineStr"/>
+      <c r="O24" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">KATRIN DUPLANTIER      	2nd payment	BGC	</t>
         </is>
@@ -17140,7 +17179,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N25" s="34" t="inlineStr">
+      <c r="N25" s="34" t="inlineStr"/>
+      <c r="O25" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">TOVE YANKOVIC          	Yankovic	BGC	</t>
         </is>
@@ -17198,7 +17238,8 @@
           <t>matches expected</t>
         </is>
       </c>
-      <c r="N26" s="34" t="inlineStr">
+      <c r="N26" s="34" t="inlineStr"/>
+      <c r="O26" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">STEFAN BERGQVIST       	BERGQV2026-009	BGC	</t>
         </is>
@@ -17252,7 +17293,8 @@
         </is>
       </c>
       <c r="M27" s="39" t="inlineStr"/>
-      <c r="N27" s="34" t="inlineStr">
+      <c r="N27" s="34" t="inlineStr"/>
+      <c r="O27" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ROSALIND NAKASHIMA-PELL	2025-641	BGC	</t>
         </is>
@@ -17310,7 +17352,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N28" s="34" t="inlineStr">
+      <c r="N28" s="34" t="inlineStr"/>
+      <c r="O28" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">MARGIT NWACHUKWU       	Giulia	BGC	</t>
         </is>
@@ -17368,7 +17411,8 @@
           <t>JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N29" s="25" t="inlineStr">
+      <c r="N29" s="25" t="inlineStr"/>
+      <c r="O29" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">KATRIN BEAUCHAMP       	2026-008	BGC	</t>
         </is>
@@ -17426,7 +17470,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N30" s="34" t="inlineStr">
+      <c r="N30" s="34" t="inlineStr"/>
+      <c r="O30" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ULRICH QUILLIAM        	school fees	BGC	</t>
         </is>
@@ -17486,6 +17531,11 @@
       </c>
       <c r="N31" s="34" t="inlineStr">
         <is>
+          <t>bank truncated the reference field</t>
+        </is>
+      </c>
+      <c r="O31" s="34" t="inlineStr">
+        <is>
           <t xml:space="preserve">LUDOVIC THIBODEAUX     	Thibodeaux fees	BGC	</t>
         </is>
       </c>
@@ -17542,7 +17592,8 @@
           <t>JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N32" s="25" t="inlineStr">
+      <c r="N32" s="25" t="inlineStr"/>
+      <c r="O32" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">ULRICH TREVELYAN       	Trevelyan	BGC	</t>
         </is>
@@ -17600,7 +17651,8 @@
           <t>matches expected</t>
         </is>
       </c>
-      <c r="N33" s="34" t="inlineStr">
+      <c r="N33" s="34" t="inlineStr"/>
+      <c r="O33" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">PASCAL HALVORSEN       	HALVOR2026-022	BGC	</t>
         </is>
@@ -17660,6 +17712,11 @@
       </c>
       <c r="N34" s="34" t="inlineStr">
         <is>
+          <t>bank truncated the reference field</t>
+        </is>
+      </c>
+      <c r="O34" s="34" t="inlineStr">
+        <is>
           <t xml:space="preserve">PASCAL GRIMALDSEN      	Grimaldsen fees	BGC	</t>
         </is>
       </c>
@@ -17716,7 +17773,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N35" s="34" t="inlineStr">
+      <c r="N35" s="34" t="inlineStr"/>
+      <c r="O35" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">TOVE FITZHUGH          	2026-019	BGC	</t>
         </is>
@@ -17774,7 +17832,8 @@
           <t>JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N36" s="49" t="inlineStr">
+      <c r="N36" s="49" t="inlineStr"/>
+      <c r="O36" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">GENEVIEVE HOLLINGWORTH 	2026-024	BGC	</t>
         </is>
@@ -17832,7 +17891,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N37" s="34" t="inlineStr">
+      <c r="N37" s="34" t="inlineStr"/>
+      <c r="O37" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">HUGO WOJCIECHOWSKI     	048	BGC	</t>
         </is>
@@ -17890,7 +17950,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N38" s="34" t="inlineStr">
+      <c r="N38" s="34" t="inlineStr"/>
+      <c r="O38" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">GENEVIEVE KILBRIDE     	2026-027	BGC	</t>
         </is>
@@ -17948,7 +18009,8 @@
           <t>JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N39" s="34" t="inlineStr">
+      <c r="N39" s="34" t="inlineStr"/>
+      <c r="O39" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ZORA ZIMMERLI          	2025-574	BGC	</t>
         </is>
@@ -18006,7 +18068,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N40" s="34" t="inlineStr">
+      <c r="N40" s="34" t="inlineStr"/>
+      <c r="O40" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">CAMILLE SIGURDSSON     	2nd payment	BGC	</t>
         </is>
@@ -18064,7 +18127,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N41" s="34" t="inlineStr">
+      <c r="N41" s="34" t="inlineStr"/>
+      <c r="O41" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">MARGIT GAILLARD        	Gaillard	BGC	</t>
         </is>
@@ -18122,7 +18186,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N42" s="34" t="inlineStr">
+      <c r="N42" s="34" t="inlineStr"/>
+      <c r="O42" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ZORA MARCHETTI         	2026-031	BGC	</t>
         </is>
@@ -18182,6 +18247,11 @@
       </c>
       <c r="N43" s="34" t="inlineStr">
         <is>
+          <t>bank truncated the reference field</t>
+        </is>
+      </c>
+      <c r="O43" s="34" t="inlineStr">
+        <is>
           <t xml:space="preserve">CAMILLE LINDQVIST      	LINDQVIST FRENCH SCHO	BGC	</t>
         </is>
       </c>
@@ -18238,7 +18308,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N44" s="34" t="inlineStr">
+      <c r="N44" s="34" t="inlineStr"/>
+      <c r="O44" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">KATRIN CASTELLANE      	2026-056	BGC	</t>
         </is>
@@ -18287,12 +18358,13 @@
           <t>no roster surname or child name (from the bank-sheet note, not the memo)</t>
         </is>
       </c>
-      <c r="M45" s="30" t="inlineStr">
+      <c r="M45" s="30" t="inlineStr"/>
+      <c r="N45" s="25" t="inlineStr">
         <is>
           <t>outflow / refund; bank truncated the reference field</t>
         </is>
       </c>
-      <c r="N45" s="25" t="inlineStr">
+      <c r="O45" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">REFUND                 	withdrawal refund	BGC	</t>
         </is>
@@ -18350,7 +18422,8 @@
           <t>half of expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N46" s="34" t="inlineStr">
+      <c r="N46" s="34" t="inlineStr"/>
+      <c r="O46" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">LUDOVIC THIBODEAUX     	Thibodeaux 2nd	BGC	</t>
         </is>
@@ -18408,7 +18481,8 @@
           <t>half of expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N47" s="34" t="inlineStr">
+      <c r="N47" s="34" t="inlineStr"/>
+      <c r="O47" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ZORA ZIMMERLI          	2nd payment	BGC	</t>
         </is>
@@ -18466,7 +18540,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N48" s="34" t="inlineStr">
+      <c r="N48" s="34" t="inlineStr"/>
+      <c r="O48" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">FERGUS DARRIEUSSECQ    	Darrieussecq	BGC	</t>
         </is>
@@ -18524,7 +18599,8 @@
           <t>JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N49" s="25" t="inlineStr">
+      <c r="N49" s="25" t="inlineStr"/>
+      <c r="O49" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">YOLANDE ACHTERBERG     	Achterberg	BGC	</t>
         </is>
@@ -18582,7 +18658,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N50" s="34" t="inlineStr">
+      <c r="N50" s="34" t="inlineStr"/>
+      <c r="O50" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">INGRID ABARCA          	2026-004	BGC	</t>
         </is>
@@ -18640,7 +18717,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N51" s="34" t="inlineStr">
+      <c r="N51" s="34" t="inlineStr"/>
+      <c r="O51" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">JEROME JANKOWSKI       	2026025	BGC	</t>
         </is>
@@ -18698,7 +18776,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N52" s="34" t="inlineStr">
+      <c r="N52" s="34" t="inlineStr"/>
+      <c r="O52" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">STEFAN BOSANQUET       	053	BGC	</t>
         </is>
@@ -18756,7 +18835,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N53" s="34" t="inlineStr">
+      <c r="N53" s="34" t="inlineStr"/>
+      <c r="O53" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">PASCAL IBARRA          	2026-024	BGC	</t>
         </is>
@@ -18814,7 +18894,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N54" s="34" t="inlineStr">
+      <c r="N54" s="34" t="inlineStr"/>
+      <c r="O54" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">MARGIT WENDELIN        	2026-047	BGC	</t>
         </is>
@@ -18872,7 +18953,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N55" s="34" t="inlineStr">
+      <c r="N55" s="34" t="inlineStr"/>
+      <c r="O55" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ROSALIND GRYNBERG      	Grynberg fees	BGC	</t>
         </is>
@@ -18930,7 +19012,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N56" s="34" t="inlineStr">
+      <c r="N56" s="34" t="inlineStr"/>
+      <c r="O56" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">CAMILLE LACHAPELLE     	LACHAP2026-028	BGC	</t>
         </is>
@@ -18988,7 +19071,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N57" s="34" t="inlineStr">
+      <c r="N57" s="34" t="inlineStr"/>
+      <c r="O57" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">DERMOT AUCLAIR         	2026-054	BGC	</t>
         </is>
@@ -19046,7 +19130,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N58" s="34" t="inlineStr">
+      <c r="N58" s="34" t="inlineStr"/>
+      <c r="O58" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">HUGO SANDOVAL          	2026-040	BGC	</t>
         </is>
@@ -19104,7 +19189,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N59" s="34" t="inlineStr">
+      <c r="N59" s="34" t="inlineStr"/>
+      <c r="O59" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">TOVE FITZHUGH          	Fitzhugh 2nd	BGC	</t>
         </is>
@@ -19162,7 +19248,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N60" s="34" t="inlineStr">
+      <c r="N60" s="34" t="inlineStr"/>
+      <c r="O60" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ELODIE ROCHETEAU       	039	BGC	</t>
         </is>
@@ -19220,7 +19307,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N61" s="34" t="inlineStr">
+      <c r="N61" s="34" t="inlineStr"/>
+      <c r="O61" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">JEROME JANKOWSKI       	2nd payment	BGC	</t>
         </is>
@@ -19274,7 +19362,8 @@
         </is>
       </c>
       <c r="M62" s="39" t="inlineStr"/>
-      <c r="N62" s="34" t="inlineStr">
+      <c r="N62" s="34" t="inlineStr"/>
+      <c r="O62" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">CAMILLE FERREIRO       	2025-503	BGC	</t>
         </is>
@@ -19332,7 +19421,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N63" s="34" t="inlineStr">
+      <c r="N63" s="34" t="inlineStr"/>
+      <c r="O63" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ADRIEN ACHTERBERG-MARCH	2026-001	BGC	</t>
         </is>
@@ -19390,7 +19480,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N64" s="34" t="inlineStr">
+      <c r="N64" s="34" t="inlineStr"/>
+      <c r="O64" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">STEFAN BOSANQUET       	2026-053	BGC	</t>
         </is>
@@ -19450,6 +19541,11 @@
       </c>
       <c r="N65" s="34" t="inlineStr">
         <is>
+          <t>prior-term ref but 2026-term amount and date  -  parent may have reused old reference</t>
+        </is>
+      </c>
+      <c r="O65" s="34" t="inlineStr">
+        <is>
           <t xml:space="preserve">JEROME PERREAULT       	2025-641	BGC	</t>
         </is>
       </c>
@@ -19506,7 +19602,8 @@
           <t>matches expected</t>
         </is>
       </c>
-      <c r="N66" s="34" t="inlineStr">
+      <c r="N66" s="34" t="inlineStr"/>
+      <c r="O66" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">PASCAL BRANNIGAN       	Brannigan	BGC	</t>
         </is>
@@ -19564,7 +19661,8 @@
           <t>JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N67" s="49" t="inlineStr">
+      <c r="N67" s="49" t="inlineStr"/>
+      <c r="O67" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">MARGIT BELHADJ-TREVELYA	2026-003	BGC	</t>
         </is>
@@ -19624,6 +19722,11 @@
       </c>
       <c r="N68" s="25" t="inlineStr">
         <is>
+          <t>bank truncated the reference field</t>
+        </is>
+      </c>
+      <c r="O68" s="25" t="inlineStr">
+        <is>
           <t xml:space="preserve">TOVE CHIDOZIE          	CHIDOZIE FRENCH SCHOO	BGC	</t>
         </is>
       </c>
@@ -19680,7 +19783,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N69" s="34" t="inlineStr">
+      <c r="N69" s="34" t="inlineStr"/>
+      <c r="O69" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">CAMILLE LACHAPELLE     	2026-028	BGC	</t>
         </is>
@@ -19740,6 +19844,11 @@
       </c>
       <c r="N70" s="34" t="inlineStr">
         <is>
+          <t>bank truncated the reference field</t>
+        </is>
+      </c>
+      <c r="O70" s="34" t="inlineStr">
+        <is>
           <t xml:space="preserve">ULRICH CARDOSO         	CARDOSO FRENCH SCHOOL	BGC	</t>
         </is>
       </c>
@@ -19796,7 +19905,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N71" s="34" t="inlineStr">
+      <c r="N71" s="34" t="inlineStr"/>
+      <c r="O71" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">INGRID BAPTISTE        	2026-006	BGC	</t>
         </is>
@@ -19856,6 +19966,11 @@
       </c>
       <c r="N72" s="34" t="inlineStr">
         <is>
+          <t>bank truncated the reference field</t>
+        </is>
+      </c>
+      <c r="O72" s="34" t="inlineStr">
+        <is>
           <t xml:space="preserve">NILS BLOMFIELD         	BLOMFIELD FRENCH SCHO	BGC	</t>
         </is>
       </c>
@@ -19912,7 +20027,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N73" s="34" t="inlineStr">
+      <c r="N73" s="34" t="inlineStr"/>
+      <c r="O73" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ELODIE KACZMAREK       	2026026	BGC	</t>
         </is>
@@ -19970,7 +20086,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N74" s="34" t="inlineStr">
+      <c r="N74" s="34" t="inlineStr"/>
+      <c r="O74" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ZORA COMEAU            	COMEAU2026-013	BGC	</t>
         </is>
@@ -20028,7 +20145,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N75" s="34" t="inlineStr">
+      <c r="N75" s="34" t="inlineStr"/>
+      <c r="O75" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">NILS ZABALA            	2026-050	BGC	</t>
         </is>
@@ -20086,7 +20204,8 @@
           <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N76" s="34" t="inlineStr">
+      <c r="N76" s="34" t="inlineStr"/>
+      <c r="O76" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">GENEVIEVE UCHENDU      	2026-044	BGC	</t>
         </is>
@@ -20144,7 +20263,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N77" s="34" t="inlineStr">
+      <c r="N77" s="34" t="inlineStr"/>
+      <c r="O77" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">FERGUS DARRIEUSSECQ    	2026-014	BGC	</t>
         </is>
@@ -20198,7 +20318,8 @@
         </is>
       </c>
       <c r="M78" s="30" t="inlineStr"/>
-      <c r="N78" s="25" t="inlineStr">
+      <c r="N78" s="25" t="inlineStr"/>
+      <c r="O78" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">MARGIT PELLETIER       	2025-627	BGC	</t>
         </is>
@@ -20256,7 +20377,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N79" s="34" t="inlineStr">
+      <c r="N79" s="34" t="inlineStr"/>
+      <c r="O79" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">CAMILLE FERREIRO       	Ferreiro 2nd	BGC	</t>
         </is>
@@ -20314,7 +20436,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N80" s="25" t="inlineStr">
+      <c r="N80" s="25" t="inlineStr"/>
+      <c r="O80" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">TOVE CHIDOZIE          	Chidozie	BGC	</t>
         </is>
@@ -20368,7 +20491,8 @@
         </is>
       </c>
       <c r="M81" s="30" t="inlineStr"/>
-      <c r="N81" s="25" t="inlineStr">
+      <c r="N81" s="25" t="inlineStr"/>
+      <c r="O81" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">MARGIT PELLETIER       	Pelletier 2nd	BGC	</t>
         </is>
@@ -20426,7 +20550,8 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N82" s="34" t="inlineStr">
+      <c r="N82" s="34" t="inlineStr"/>
+      <c r="O82" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">NILS ZABALA            	Zabala 2nd	BGC	</t>
         </is>
@@ -20484,14 +20609,15 @@
           <t>half of expected</t>
         </is>
       </c>
-      <c r="N83" s="34" t="inlineStr">
+      <c r="N83" s="34" t="inlineStr"/>
+      <c r="O83" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">INGRID BAPTISTE        	Baptiste	BGC	</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N83"/>
+  <autoFilter ref="A3:O83"/>
   <conditionalFormatting sqref="A4:N83">
     <cfRule type="expression" priority="1" dxfId="5">
       <formula>$I4="X"</formula>
@@ -20532,7 +20658,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Review queue  -  receipts the engine would not allocate. Decide, then type the family ID into Receipts column M (row shown) and re-run.</t>
+          <t>Review queue  -  receipts the engine would not allocate. Decide, then type the family ID into Receipts column F (row shown) and re-run.</t>
         </is>
       </c>
     </row>

--- a/examples/fee_ledger.xlsx
+++ b/examples/fee_ledger.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Families'!$A$3:$H$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Children'!$A$3:$V$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Receipts'!$A$3:$O$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Review'!$A$3:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Review'!$A$3:$K$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="B2" s="24" t="n">
-        <v>46271</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="4">
@@ -1308,7 +1308,7 @@
       <c r="L7" s="30" t="inlineStr"/>
       <c r="M7" s="30" t="inlineStr">
         <is>
-          <t>3 receipt(s) in Review name this family; £767.50 tagged AUT-2025 looks like a JAN-2026 payment</t>
+          <t>1 receipt(s) in Review name this family; £767.50 tagged AUT-2025 looks like a JAN-2026 payment</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>FAM-045</t>
+          <t>FAM-056</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>PELLETIER</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="C15" s="25" t="n">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>2026-008</t>
+          <t>2026-046</t>
         </is>
       </c>
       <c r="E15" s="26">
@@ -1718,19 +1718,19 @@
       <c r="L15" s="30" t="inlineStr"/>
       <c r="M15" s="30" t="inlineStr">
         <is>
-          <t>3 receipt(s) in Review name this family</t>
+          <t>£409.50 tagged AUT-2025 looks like a JAN-2026 payment</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>FAM-056</t>
+          <t>FAM-048</t>
         </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>RASMUSSEN</t>
         </is>
       </c>
       <c r="C16" s="25" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>2026-046</t>
+          <t>2026-038</t>
         </is>
       </c>
       <c r="E16" s="26">
@@ -1761,27 +1761,33 @@
         <f>COUNTIFS(Receipts!$G$4:$G$600,$A16,Receipts!$E$4:$E$600,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="J16" s="29" t="inlineStr"/>
+      <c r="J16" s="29" t="n">
+        <v>46059</v>
+      </c>
       <c r="K16" s="28">
         <f>IF($G16&gt;0.5,$B$2-Terms!$G$5,"")</f>
         <v/>
       </c>
-      <c r="L16" s="30" t="inlineStr"/>
+      <c r="L16" s="30" t="inlineStr">
+        <is>
+          <t>Rasmussen</t>
+        </is>
+      </c>
       <c r="M16" s="30" t="inlineStr">
         <is>
-          <t>£409.50 tagged AUT-2025 looks like a JAN-2026 payment</t>
+          <t>1 receipt(s) in Review name this family</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="25" t="inlineStr">
         <is>
-          <t>FAM-048</t>
+          <t>FAM-025</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>RASMUSSEN</t>
+          <t>FERREIRO</t>
         </is>
       </c>
       <c r="C17" s="25" t="n">
@@ -1789,7 +1795,7 @@
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>2026-038</t>
+          <t>2026-058</t>
         </is>
       </c>
       <c r="E17" s="26">
@@ -1813,7 +1819,7 @@
         <v/>
       </c>
       <c r="J17" s="29" t="n">
-        <v>46059</v>
+        <v>46144</v>
       </c>
       <c r="K17" s="28">
         <f>IF($G17&gt;0.5,$B$2-Terms!$G$5,"")</f>
@@ -1821,24 +1827,24 @@
       </c>
       <c r="L17" s="30" t="inlineStr">
         <is>
-          <t>Rasmussen</t>
+          <t>Ferreiro 2nd</t>
         </is>
       </c>
       <c r="M17" s="30" t="inlineStr">
         <is>
-          <t>1 receipt(s) in Review name this family</t>
+          <t>£217.25 tagged AUT-2025 looks like a JAN-2026 payment</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>FAM-025</t>
+          <t>FAM-021</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>FERREIRO</t>
+          <t>DUPLANTIER</t>
         </is>
       </c>
       <c r="C18" s="25" t="n">
@@ -1846,7 +1852,7 @@
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>2026-058</t>
+          <t>2026-016</t>
         </is>
       </c>
       <c r="E18" s="26">
@@ -1870,7 +1876,7 @@
         <v/>
       </c>
       <c r="J18" s="29" t="n">
-        <v>46144</v>
+        <v>46064</v>
       </c>
       <c r="K18" s="28">
         <f>IF($G18&gt;0.5,$B$2-Terms!$G$5,"")</f>
@@ -1878,24 +1884,24 @@
       </c>
       <c r="L18" s="30" t="inlineStr">
         <is>
-          <t>Ferreiro 2nd</t>
+          <t>2nd payment</t>
         </is>
       </c>
       <c r="M18" s="30" t="inlineStr">
         <is>
-          <t>£217.25 tagged AUT-2025 looks like a JAN-2026 payment</t>
+          <t>£204.75 tagged AUT-2025 looks like a JAN-2026 payment</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>FAM-021</t>
+          <t>FAM-061</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>DUPLANTIER</t>
+          <t>ZIMMERLI</t>
         </is>
       </c>
       <c r="C19" s="25" t="n">
@@ -1903,7 +1909,7 @@
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>2026-016</t>
+          <t>2026-051</t>
         </is>
       </c>
       <c r="E19" s="26">
@@ -1927,7 +1933,7 @@
         <v/>
       </c>
       <c r="J19" s="29" t="n">
-        <v>46064</v>
+        <v>46101</v>
       </c>
       <c r="K19" s="28">
         <f>IF($G19&gt;0.5,$B$2-Terms!$G$5,"")</f>
@@ -1945,189 +1951,185 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>FAM-061</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>ZIMMERLI</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="n">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>FAM-001</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>ABARCA</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>2026-051</t>
-        </is>
-      </c>
-      <c r="E20" s="26">
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>2026-004</t>
+        </is>
+      </c>
+      <c r="E20" s="35">
         <f>SUMIFS(Children!$R$4:$R$500,Children!$B$4:$B$500,$A20,Children!$F$4:$F$500,"Enrolled",Children!$G$4:$G$500,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="35">
         <f>SUMIFS(Receipts!$B$4:$B$600,Receipts!$G$4:$G$600,$A20,Receipts!$E$4:$E$600,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="35">
         <f>$E20-$F20</f>
         <v/>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="36">
         <f>IF($E20=0,"no charge",IF($F20&lt;=0,"unpaid",IF(ABS($G20)&lt;=0.5,"settled",IF($G20&gt;0,"part paid","overpaid"))))</f>
         <v/>
       </c>
-      <c r="I20" s="28">
+      <c r="I20" s="37">
         <f>COUNTIFS(Receipts!$G$4:$G$600,$A20,Receipts!$E$4:$E$600,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="J20" s="29" t="n">
-        <v>46101</v>
-      </c>
-      <c r="K20" s="28">
+      <c r="J20" s="38" t="n">
+        <v>46103</v>
+      </c>
+      <c r="K20" s="37">
         <f>IF($G20&gt;0.5,$B$2-Terms!$G$5,"")</f>
         <v/>
       </c>
-      <c r="L20" s="30" t="inlineStr">
-        <is>
-          <t>2nd payment</t>
-        </is>
-      </c>
-      <c r="M20" s="30" t="inlineStr">
-        <is>
-          <t>£204.75 tagged AUT-2025 looks like a JAN-2026 payment</t>
-        </is>
-      </c>
+      <c r="L20" s="39" t="inlineStr">
+        <is>
+          <t>2026-004</t>
+        </is>
+      </c>
+      <c r="M20" s="39" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>FAM-001</t>
-        </is>
-      </c>
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>ABARCA</t>
-        </is>
-      </c>
-      <c r="C21" s="34" t="n">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>FAM-003</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>ACHTERBERG-MARCHETTI</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="34" t="inlineStr">
-        <is>
-          <t>2026-004</t>
-        </is>
-      </c>
-      <c r="E21" s="35">
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>2026-001</t>
+        </is>
+      </c>
+      <c r="E21" s="26">
         <f>SUMIFS(Children!$R$4:$R$500,Children!$B$4:$B$500,$A21,Children!$F$4:$F$500,"Enrolled",Children!$G$4:$G$500,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="26">
         <f>SUMIFS(Receipts!$B$4:$B$600,Receipts!$G$4:$G$600,$A21,Receipts!$E$4:$E$600,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="26">
         <f>$E21-$F21</f>
         <v/>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="27">
         <f>IF($E21=0,"no charge",IF($F21&lt;=0,"unpaid",IF(ABS($G21)&lt;=0.5,"settled",IF($G21&gt;0,"part paid","overpaid"))))</f>
         <v/>
       </c>
-      <c r="I21" s="37">
+      <c r="I21" s="28">
         <f>COUNTIFS(Receipts!$G$4:$G$600,$A21,Receipts!$E$4:$E$600,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="J21" s="38" t="n">
-        <v>46103</v>
-      </c>
-      <c r="K21" s="37">
+      <c r="J21" s="29" t="n">
+        <v>46129</v>
+      </c>
+      <c r="K21" s="28">
         <f>IF($G21&gt;0.5,$B$2-Terms!$G$5,"")</f>
         <v/>
       </c>
-      <c r="L21" s="39" t="inlineStr">
-        <is>
-          <t>2026-004</t>
-        </is>
-      </c>
-      <c r="M21" s="39" t="inlineStr"/>
+      <c r="L21" s="30" t="inlineStr">
+        <is>
+          <t>2026-001</t>
+        </is>
+      </c>
+      <c r="M21" s="30" t="inlineStr">
+        <is>
+          <t>1 receipt(s) in Review name this family</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>FAM-003</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>ACHTERBERG-MARCHETTI</t>
-        </is>
-      </c>
-      <c r="C22" s="25" t="n">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>FAM-004</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>ASHWORTH</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>2026-001</t>
-        </is>
-      </c>
-      <c r="E22" s="26">
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="E22" s="35">
         <f>SUMIFS(Children!$R$4:$R$500,Children!$B$4:$B$500,$A22,Children!$F$4:$F$500,"Enrolled",Children!$G$4:$G$500,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="35">
         <f>SUMIFS(Receipts!$B$4:$B$600,Receipts!$G$4:$G$600,$A22,Receipts!$E$4:$E$600,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="35">
         <f>$E22-$F22</f>
         <v/>
       </c>
-      <c r="H22" s="27">
+      <c r="H22" s="36">
         <f>IF($E22=0,"no charge",IF($F22&lt;=0,"unpaid",IF(ABS($G22)&lt;=0.5,"settled",IF($G22&gt;0,"part paid","overpaid"))))</f>
         <v/>
       </c>
-      <c r="I22" s="28">
+      <c r="I22" s="37">
         <f>COUNTIFS(Receipts!$G$4:$G$600,$A22,Receipts!$E$4:$E$600,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="J22" s="29" t="n">
-        <v>46129</v>
-      </c>
-      <c r="K22" s="28">
+      <c r="J22" s="38" t="n">
+        <v>46044</v>
+      </c>
+      <c r="K22" s="37">
         <f>IF($G22&gt;0.5,$B$2-Terms!$G$5,"")</f>
         <v/>
       </c>
-      <c r="L22" s="30" t="inlineStr">
-        <is>
-          <t>2026-001</t>
-        </is>
-      </c>
-      <c r="M22" s="30" t="inlineStr">
-        <is>
-          <t>1 receipt(s) in Review name this family</t>
-        </is>
-      </c>
+      <c r="L22" s="39" t="inlineStr">
+        <is>
+          <t>ASHWORTH FRENCH SCHOO</t>
+        </is>
+      </c>
+      <c r="M22" s="39" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="34" t="inlineStr">
         <is>
-          <t>FAM-004</t>
+          <t>FAM-005</t>
         </is>
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>ASHWORTH</t>
+          <t>AUCLAIR</t>
         </is>
       </c>
       <c r="C23" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="34" t="inlineStr">
         <is>
-          <t>2026-005</t>
+          <t>2026-054</t>
         </is>
       </c>
       <c r="E23" s="35">
@@ -2151,7 +2153,7 @@
         <v/>
       </c>
       <c r="J23" s="38" t="n">
-        <v>46044</v>
+        <v>46116</v>
       </c>
       <c r="K23" s="37">
         <f>IF($G23&gt;0.5,$B$2-Terms!$G$5,"")</f>
@@ -2159,7 +2161,7 @@
       </c>
       <c r="L23" s="39" t="inlineStr">
         <is>
-          <t>ASHWORTH FRENCH SCHOO</t>
+          <t>2026-054</t>
         </is>
       </c>
       <c r="M23" s="39" t="inlineStr"/>
@@ -2167,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="34" t="inlineStr">
         <is>
-          <t>FAM-005</t>
+          <t>FAM-006</t>
         </is>
       </c>
       <c r="B24" s="34" t="inlineStr">
         <is>
-          <t>AUCLAIR</t>
+          <t>BAPTISTE</t>
         </is>
       </c>
       <c r="C24" s="34" t="n">
@@ -2180,7 +2182,7 @@
       </c>
       <c r="D24" s="34" t="inlineStr">
         <is>
-          <t>2026-054</t>
+          <t>2026-006</t>
         </is>
       </c>
       <c r="E24" s="35">
@@ -2204,7 +2206,7 @@
         <v/>
       </c>
       <c r="J24" s="38" t="n">
-        <v>46116</v>
+        <v>46182</v>
       </c>
       <c r="K24" s="37">
         <f>IF($G24&gt;0.5,$B$2-Terms!$G$5,"")</f>
@@ -2212,63 +2214,67 @@
       </c>
       <c r="L24" s="39" t="inlineStr">
         <is>
-          <t>2026-054</t>
+          <t>2026-006 | Baptiste</t>
         </is>
       </c>
       <c r="M24" s="39" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
-        <is>
-          <t>FAM-006</t>
-        </is>
-      </c>
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>BAPTISTE</t>
-        </is>
-      </c>
-      <c r="C25" s="34" t="n">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>FAM-008</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>BELHADJ</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="34" t="inlineStr">
-        <is>
-          <t>2026-006</t>
-        </is>
-      </c>
-      <c r="E25" s="35">
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>2026-008</t>
+        </is>
+      </c>
+      <c r="E25" s="26">
         <f>SUMIFS(Children!$R$4:$R$500,Children!$B$4:$B$500,$A25,Children!$F$4:$F$500,"Enrolled",Children!$G$4:$G$500,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="26">
         <f>SUMIFS(Receipts!$B$4:$B$600,Receipts!$G$4:$G$600,$A25,Receipts!$E$4:$E$600,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="26">
         <f>$E25-$F25</f>
         <v/>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="27">
         <f>IF($E25=0,"no charge",IF($F25&lt;=0,"unpaid",IF(ABS($G25)&lt;=0.5,"settled",IF($G25&gt;0,"part paid","overpaid"))))</f>
         <v/>
       </c>
-      <c r="I25" s="37">
+      <c r="I25" s="28">
         <f>COUNTIFS(Receipts!$G$4:$G$600,$A25,Receipts!$E$4:$E$600,"JAN-2026")</f>
         <v/>
       </c>
-      <c r="J25" s="38" t="n">
-        <v>46182</v>
-      </c>
-      <c r="K25" s="37">
+      <c r="J25" s="29" t="n">
+        <v>46070</v>
+      </c>
+      <c r="K25" s="28">
         <f>IF($G25&gt;0.5,$B$2-Terms!$G$5,"")</f>
         <v/>
       </c>
-      <c r="L25" s="39" t="inlineStr">
-        <is>
-          <t>2026-006 | Baptiste</t>
-        </is>
-      </c>
-      <c r="M25" s="39" t="inlineStr"/>
+      <c r="L25" s="30" t="inlineStr">
+        <is>
+          <t>2026-008</t>
+        </is>
+      </c>
+      <c r="M25" s="30" t="inlineStr">
+        <is>
+          <t>1 receipt(s) in Review name this family</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="34" t="inlineStr">
@@ -4295,16 +4301,16 @@
     <row r="64">
       <c r="A64" s="25" t="inlineStr">
         <is>
-          <t>FAM-008</t>
+          <t>FAM-045</t>
         </is>
       </c>
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>BELHADJ</t>
+          <t>PELLETIER</t>
         </is>
       </c>
       <c r="C64" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
@@ -4332,7 +4338,7 @@
         <v/>
       </c>
       <c r="J64" s="29" t="n">
-        <v>46042</v>
+        <v>46170</v>
       </c>
       <c r="K64" s="28">
         <f>IF($G64&gt;0.5,$B$2-Terms!$G$5,"")</f>
@@ -4340,12 +4346,12 @@
       </c>
       <c r="L64" s="30" t="inlineStr">
         <is>
-          <t>2026-008</t>
+          <t>2026-008 | Pelletier 2nd</t>
         </is>
       </c>
       <c r="M64" s="30" t="inlineStr">
         <is>
-          <t>2 receipt(s) in Review name this family</t>
+          <t>£204.75 tagged AUT-2025 looks like a JAN-2026 payment</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4530,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>The autumn invoice register was never supplied, so autumn receipts can be tied to a family but not to an invoice.</t>
+          <t>The AUT-2025 invoice register was never supplied, so AUT-2025 receipts can be tied to a family but not to an invoice.</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4554,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1 enrolled children have no invoice number and no fee. Two of them have payment notes, so money may have arrived with nothing to match it to.</t>
+          <t>1 enrolled child has no invoice number and no fee. That child has a payment note on the roster, so money may have arrived with nothing to match it to.</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4568,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>One invoice charges £18 supplies instead of £25  -  the only invoice the fee rules cannot reproduce.</t>
+          <t>1 invoice whose add-ons or discount the fee rules cannot reproduce. The Check column on Children also recomputes tuition from sessions and sibling count, so it can flag rows this count does not.</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4612,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Fee rules  -  inputs (blue). Source: charity price list, January 2026 (photo supplied by user).</t>
+          <t>Fee rules  -  inputs (blue). Source: school price list, January 2026.</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6397,11 @@
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr"/>
-      <c r="G48" s="40" t="inlineStr"/>
+      <c r="G48" s="40" t="inlineStr">
+        <is>
+          <t>MARGIT PELLETIER</t>
+        </is>
+      </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
           <t>invoice number shared with another family  -  2026-008</t>
@@ -16121,11 +16131,11 @@
         <v>46042</v>
       </c>
       <c r="B8" s="46" t="n">
-        <v>1184</v>
+        <v>409.5</v>
       </c>
       <c r="C8" s="34" t="inlineStr">
         <is>
-          <t>GENEVIEVE BELHADJ</t>
+          <t>MARGIT PELLETIER</t>
         </is>
       </c>
       <c r="D8" s="34" t="inlineStr">
@@ -16154,7 +16164,7 @@
       </c>
       <c r="J8" s="39" t="inlineStr">
         <is>
-          <t>FAM-008</t>
+          <t>FAM-045</t>
         </is>
       </c>
       <c r="K8" s="39" t="inlineStr"/>
@@ -16165,13 +16175,13 @@
       </c>
       <c r="M8" s="39" t="inlineStr">
         <is>
-          <t>unusual (expected £774.50)</t>
+          <t>matches expected; JAN-2026 amount</t>
         </is>
       </c>
       <c r="N8" s="34" t="inlineStr"/>
       <c r="O8" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve">GENEVIEVE BELHADJ      	2026-008	BGC	</t>
+          <t xml:space="preserve">MARGIT PELLETIER       	2026-008	BGC	</t>
         </is>
       </c>
     </row>
@@ -16349,7 +16359,11 @@
           <t>JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N11" s="34" t="inlineStr"/>
+      <c r="N11" s="34" t="inlineStr">
+        <is>
+          <t>prior-term ref but JAN-2026 amount and date  -  parent may have reused old reference</t>
+        </is>
+      </c>
       <c r="O11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">KATRIN DUPLANTIER      	2025-608	BGC	</t>
@@ -16646,7 +16660,7 @@
       </c>
       <c r="N16" s="34" t="inlineStr">
         <is>
-          <t>prior-term ref but 2026-term amount and date  -  parent may have reused old reference</t>
+          <t>prior-term ref but JAN-2026 amount and date  -  parent may have reused old reference</t>
         </is>
       </c>
       <c r="O16" s="34" t="inlineStr">
@@ -16762,7 +16776,11 @@
         </is>
       </c>
       <c r="M18" s="39" t="inlineStr"/>
-      <c r="N18" s="34" t="inlineStr"/>
+      <c r="N18" s="34" t="inlineStr">
+        <is>
+          <t>prior-term ref but JAN-2026 amount and date  -  parent may have reused old reference</t>
+        </is>
+      </c>
       <c r="O18" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">GENEVIEVE KILBRIDE     	2025-611	BGC	</t>
@@ -16882,7 +16900,7 @@
       </c>
       <c r="N20" s="34" t="inlineStr">
         <is>
-          <t>prior-term ref but 2026-term amount and date  -  parent may have reused old reference</t>
+          <t>prior-term ref but JAN-2026 amount and date  -  parent may have reused old reference</t>
         </is>
       </c>
       <c r="O20" s="34" t="inlineStr">
@@ -17293,7 +17311,11 @@
         </is>
       </c>
       <c r="M27" s="39" t="inlineStr"/>
-      <c r="N27" s="34" t="inlineStr"/>
+      <c r="N27" s="34" t="inlineStr">
+        <is>
+          <t>prior-term ref but JAN-2026 amount and date  -  parent may have reused old reference</t>
+        </is>
+      </c>
       <c r="O27" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ROSALIND NAKASHIMA-PELL	2025-641	BGC	</t>
@@ -17360,61 +17382,61 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="52" t="n">
+      <c r="A29" s="45" t="n">
         <v>46070</v>
       </c>
-      <c r="B29" s="53" t="n">
-        <v>434.5</v>
-      </c>
-      <c r="C29" s="25" t="inlineStr">
-        <is>
-          <t>KATRIN BEAUCHAMP</t>
-        </is>
-      </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="B29" s="46" t="n">
+        <v>774.5</v>
+      </c>
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>GENEVIEVE BELHADJ</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
         <is>
           <t>2026-008</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E29" s="34" t="inlineStr">
         <is>
           <t>JAN-2026</t>
         </is>
       </c>
-      <c r="F29" s="27" t="inlineStr"/>
-      <c r="G29" s="27">
+      <c r="F29" s="36" t="inlineStr"/>
+      <c r="G29" s="36">
         <f>IF($F29&lt;&gt;"",$F29,$J29)</f>
         <v/>
       </c>
-      <c r="H29" s="27">
+      <c r="H29" s="36">
         <f>IF($G29&lt;&gt;"","yes","")</f>
         <v/>
       </c>
-      <c r="I29" s="30" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J29" s="30" t="inlineStr"/>
-      <c r="K29" s="30" t="inlineStr">
-        <is>
-          <t>FAM-008, FAM-045</t>
-        </is>
-      </c>
-      <c r="L29" s="30" t="inlineStr">
-        <is>
-          <t>reference 2026-008 is shared by FAM-008, FAM-045</t>
-        </is>
-      </c>
-      <c r="M29" s="30" t="inlineStr">
-        <is>
-          <t>JAN-2026 amount</t>
-        </is>
-      </c>
-      <c r="N29" s="25" t="inlineStr"/>
-      <c r="O29" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KATRIN BEAUCHAMP       	2026-008	BGC	</t>
+      <c r="I29" s="39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J29" s="39" t="inlineStr">
+        <is>
+          <t>FAM-008</t>
+        </is>
+      </c>
+      <c r="K29" s="39" t="inlineStr"/>
+      <c r="L29" s="39" t="inlineStr">
+        <is>
+          <t>invoice reference 2026-008</t>
+        </is>
+      </c>
+      <c r="M29" s="39" t="inlineStr">
+        <is>
+          <t>matches expected; JAN-2026 amount</t>
+        </is>
+      </c>
+      <c r="N29" s="34" t="inlineStr"/>
+      <c r="O29" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENEVIEVE BELHADJ      	2026-008	BGC	</t>
         </is>
       </c>
     </row>
@@ -18009,7 +18031,11 @@
           <t>JAN-2026 amount</t>
         </is>
       </c>
-      <c r="N39" s="34" t="inlineStr"/>
+      <c r="N39" s="34" t="inlineStr">
+        <is>
+          <t>prior-term ref but JAN-2026 amount and date  -  parent may have reused old reference</t>
+        </is>
+      </c>
       <c r="O39" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">ZORA ZIMMERLI          	2025-574	BGC	</t>
@@ -19362,7 +19388,11 @@
         </is>
       </c>
       <c r="M62" s="39" t="inlineStr"/>
-      <c r="N62" s="34" t="inlineStr"/>
+      <c r="N62" s="34" t="inlineStr">
+        <is>
+          <t>prior-term ref but JAN-2026 amount and date  -  parent may have reused old reference</t>
+        </is>
+      </c>
       <c r="O62" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">CAMILLE FERREIRO       	2025-503	BGC	</t>
@@ -19541,7 +19571,7 @@
       </c>
       <c r="N65" s="34" t="inlineStr">
         <is>
-          <t>prior-term ref but 2026-term amount and date  -  parent may have reused old reference</t>
+          <t>prior-term ref but JAN-2026 amount and date  -  parent may have reused old reference</t>
         </is>
       </c>
       <c r="O65" s="34" t="inlineStr">
@@ -19673,7 +19703,7 @@
         <v>46133</v>
       </c>
       <c r="B68" s="53" t="n">
-        <v>347</v>
+        <v>359.5</v>
       </c>
       <c r="C68" s="25" t="inlineStr">
         <is>
@@ -19717,7 +19747,7 @@
       </c>
       <c r="M68" s="30" t="inlineStr">
         <is>
-          <t>half of expected</t>
+          <t>unusual (expected £694.00)</t>
         </is>
       </c>
       <c r="N68" s="25" t="inlineStr">
@@ -20271,55 +20301,63 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="52" t="n">
+      <c r="A78" s="45" t="n">
         <v>46143</v>
       </c>
-      <c r="B78" s="53" t="n">
-        <v>592</v>
-      </c>
-      <c r="C78" s="25" t="inlineStr">
+      <c r="B78" s="46" t="n">
+        <v>204.75</v>
+      </c>
+      <c r="C78" s="34" t="inlineStr">
         <is>
           <t>MARGIT PELLETIER</t>
         </is>
       </c>
-      <c r="D78" s="25" t="inlineStr">
+      <c r="D78" s="34" t="inlineStr">
         <is>
           <t>2025-627</t>
         </is>
       </c>
-      <c r="E78" s="25" t="inlineStr">
+      <c r="E78" s="34" t="inlineStr">
         <is>
           <t>AUT-2025</t>
         </is>
       </c>
-      <c r="F78" s="27" t="inlineStr"/>
-      <c r="G78" s="27">
+      <c r="F78" s="36" t="inlineStr"/>
+      <c r="G78" s="36">
         <f>IF($F78&lt;&gt;"",$F78,$J78)</f>
         <v/>
       </c>
-      <c r="H78" s="27">
+      <c r="H78" s="36">
         <f>IF($G78&lt;&gt;"","yes","")</f>
         <v/>
       </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr"/>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>FAM-042, FAM-045</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>several families fit: FAM-042 (surname PELLETIER); FAM-045 (surname PELLETIER)</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr"/>
-      <c r="N78" s="25" t="inlineStr"/>
-      <c r="O78" s="25" t="inlineStr">
+      <c r="I78" s="39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J78" s="39" t="inlineStr">
+        <is>
+          <t>FAM-045</t>
+        </is>
+      </c>
+      <c r="K78" s="39" t="inlineStr"/>
+      <c r="L78" s="39" t="inlineStr">
+        <is>
+          <t>payer name previously seen with a verified reference for this family (prior-term reference 2025-627  -  family identified, invoice not loaded)</t>
+        </is>
+      </c>
+      <c r="M78" s="39" t="inlineStr">
+        <is>
+          <t>JAN-2026 amount</t>
+        </is>
+      </c>
+      <c r="N78" s="34" t="inlineStr">
+        <is>
+          <t>prior-term ref but JAN-2026 amount and date  -  parent may have reused old reference</t>
+        </is>
+      </c>
+      <c r="O78" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">MARGIT PELLETIER       	2025-627	BGC	</t>
         </is>
@@ -20389,7 +20427,7 @@
         <v>46168</v>
       </c>
       <c r="B80" s="53" t="n">
-        <v>347</v>
+        <v>359.5</v>
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
@@ -20433,7 +20471,7 @@
       </c>
       <c r="M80" s="30" t="inlineStr">
         <is>
-          <t>half of expected</t>
+          <t>unusual (expected £694.00)</t>
         </is>
       </c>
       <c r="N80" s="25" t="inlineStr"/>
@@ -20444,55 +20482,59 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="52" t="n">
+      <c r="A81" s="45" t="n">
         <v>46170</v>
       </c>
-      <c r="B81" s="53" t="n">
-        <v>592</v>
-      </c>
-      <c r="C81" s="25" t="inlineStr">
+      <c r="B81" s="46" t="n">
+        <v>204.75</v>
+      </c>
+      <c r="C81" s="34" t="inlineStr">
         <is>
           <t>MARGIT PELLETIER</t>
         </is>
       </c>
-      <c r="D81" s="25" t="inlineStr">
+      <c r="D81" s="34" t="inlineStr">
         <is>
           <t>Pelletier 2nd</t>
         </is>
       </c>
-      <c r="E81" s="25" t="inlineStr">
+      <c r="E81" s="34" t="inlineStr">
         <is>
           <t>JAN-2026</t>
         </is>
       </c>
-      <c r="F81" s="27" t="inlineStr"/>
-      <c r="G81" s="27">
+      <c r="F81" s="36" t="inlineStr"/>
+      <c r="G81" s="36">
         <f>IF($F81&lt;&gt;"",$F81,$J81)</f>
         <v/>
       </c>
-      <c r="H81" s="27">
+      <c r="H81" s="36">
         <f>IF($G81&lt;&gt;"","yes","")</f>
         <v/>
       </c>
-      <c r="I81" s="30" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J81" s="30" t="inlineStr"/>
-      <c r="K81" s="30" t="inlineStr">
-        <is>
-          <t>FAM-042, FAM-045</t>
-        </is>
-      </c>
-      <c r="L81" s="30" t="inlineStr">
-        <is>
-          <t>several families fit: FAM-042 (surname PELLETIER); FAM-045 (surname PELLETIER)</t>
-        </is>
-      </c>
-      <c r="M81" s="30" t="inlineStr"/>
-      <c r="N81" s="25" t="inlineStr"/>
-      <c r="O81" s="25" t="inlineStr">
+      <c r="I81" s="39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J81" s="39" t="inlineStr">
+        <is>
+          <t>FAM-045</t>
+        </is>
+      </c>
+      <c r="K81" s="39" t="inlineStr"/>
+      <c r="L81" s="39" t="inlineStr">
+        <is>
+          <t>payer name previously seen with a verified reference for this family</t>
+        </is>
+      </c>
+      <c r="M81" s="39" t="inlineStr">
+        <is>
+          <t>half of expected; JAN-2026 amount</t>
+        </is>
+      </c>
+      <c r="N81" s="34" t="inlineStr"/>
+      <c r="O81" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">MARGIT PELLETIER       	Pelletier 2nd	BGC	</t>
         </is>
@@ -20639,7 +20681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -20767,70 +20809,70 @@
       <c r="K4" s="19" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="B5" s="54" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>592</v>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>MARGIT PELLETIER</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>2025-627</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>AUT-2025</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>FAM-042 NAKASHIMA-PELLETIER, FAM-045 PELLETIER</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>several families fit: FAM-042 (surname PELLETIER); FAM-045 (surname PELLETIER)</t>
-        </is>
-      </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="A5" s="49" t="n">
+        <v>36</v>
+      </c>
+      <c r="B5" s="47" t="n">
+        <v>46077</v>
+      </c>
+      <c r="C5" s="48" t="n">
+        <v>434.5</v>
+      </c>
+      <c r="D5" s="49" t="inlineStr">
+        <is>
+          <t>GENEVIEVE HOLLINGWORTH</t>
+        </is>
+      </c>
+      <c r="E5" s="49" t="inlineStr">
+        <is>
+          <t>2026-024</t>
+        </is>
+      </c>
+      <c r="F5" s="49" t="inlineStr">
+        <is>
+          <t>JAN-2026</t>
+        </is>
+      </c>
+      <c r="G5" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H5" s="49" t="inlineStr">
+        <is>
+          <t>FAM-032 HOLLINGWORTH, FAM-033 IBARRA</t>
+        </is>
+      </c>
+      <c r="I5" s="49" t="inlineStr">
+        <is>
+          <t>reference 2026-024 points to FAM-033 but the memo names FAM-032  -  parent may have typed the wrong invoice number</t>
+        </is>
+      </c>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K5" s="19" t="inlineStr"/>
+      <c r="K5" s="48" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>46170</v>
+        <v>46103</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>592</v>
+        <v>434.5</v>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>MARGIT PELLETIER</t>
+          <t>YOLANDE ACHTERBERG</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Pelletier 2nd</t>
+          <t>Achterberg</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -20845,12 +20887,12 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>FAM-042 NAKASHIMA-PELLETIER, FAM-045 PELLETIER</t>
+          <t>FAM-002 ACHTERBERG, FAM-003 ACHTERBERG-MARCHETTI</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>several families fit: FAM-042 (surname PELLETIER); FAM-045 (surname PELLETIER)</t>
+          <t>several families fit: FAM-002 (surname ACHTERBERG); FAM-003 (surname ACHTERBERG)</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
@@ -20861,384 +20903,243 @@
       <c r="K6" s="19" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>29</v>
-      </c>
-      <c r="B7" s="54" t="n">
-        <v>46070</v>
-      </c>
-      <c r="C7" s="19" t="n">
+      <c r="A7" s="49" t="n">
+        <v>67</v>
+      </c>
+      <c r="B7" s="47" t="n">
+        <v>46133</v>
+      </c>
+      <c r="C7" s="48" t="n">
         <v>434.5</v>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>KATRIN BEAUCHAMP</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>2026-008</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="D7" s="49" t="inlineStr">
+        <is>
+          <t>MARGIT BELHADJ-TREVELYA</t>
+        </is>
+      </c>
+      <c r="E7" s="49" t="inlineStr">
+        <is>
+          <t>2026-003</t>
+        </is>
+      </c>
+      <c r="F7" s="49" t="inlineStr">
         <is>
           <t>JAN-2026</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H7" s="49" t="inlineStr">
+        <is>
+          <t>FAM-008 BELHADJ, FAM-009 BELHADJ-TREVELYAN, FAM-042 NAKASHIMA-PELLETIER</t>
+        </is>
+      </c>
+      <c r="I7" s="49" t="inlineStr">
+        <is>
+          <t>reference 2026-003 points to FAM-042 but the memo names FAM-008, FAM-009  -  parent may have typed the wrong invoice number</t>
+        </is>
+      </c>
+      <c r="J7" s="49" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="B8" s="54" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>-409.5</v>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>REFUND</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>withdrawal refund</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>JAN-2026</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>FAM-008 BELHADJ, FAM-045 PELLETIER</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>reference 2026-008 is shared by FAM-008, FAM-045</t>
-        </is>
-      </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>no roster surname or child name (from the bank-sheet note, not the memo)</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K7" s="19" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="B8" s="47" t="n">
-        <v>46077</v>
-      </c>
-      <c r="C8" s="48" t="n">
-        <v>434.5</v>
-      </c>
-      <c r="D8" s="49" t="inlineStr">
-        <is>
-          <t>GENEVIEVE HOLLINGWORTH</t>
-        </is>
-      </c>
-      <c r="E8" s="49" t="inlineStr">
-        <is>
-          <t>2026-024</t>
-        </is>
-      </c>
-      <c r="F8" s="49" t="inlineStr">
+      <c r="K8" s="19" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="n">
+        <v>68</v>
+      </c>
+      <c r="B9" s="52" t="n">
+        <v>46133</v>
+      </c>
+      <c r="C9" s="53" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>TOVE CHIDOZIE</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>CHIDOZIE FRENCH SCHOO</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>JAN-2026</t>
         </is>
       </c>
-      <c r="G8" s="49" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>FAM-017 CHIDOZIE</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="inlineStr">
+        <is>
+          <t>surname CHIDOZIE  -  chosen over FAM-016 because only this family is billed this term</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="inlineStr">
+        <is>
+          <t>unusual (expected £694.00)</t>
+        </is>
+      </c>
+      <c r="K9" s="53" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="n">
+        <v>80</v>
+      </c>
+      <c r="B10" s="52" t="n">
+        <v>46168</v>
+      </c>
+      <c r="C10" s="53" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>TOVE CHIDOZIE</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>Chidozie</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>JAN-2026</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t>FAM-017 CHIDOZIE</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t>surname CHIDOZIE  -  chosen over FAM-016 because only this family is billed this term</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="inlineStr">
+        <is>
+          <t>unusual (expected £694.00)</t>
+        </is>
+      </c>
+      <c r="K10" s="53" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="47" t="n">
+        <v>46038</v>
+      </c>
+      <c r="C11" s="48" t="n">
+        <v>229.75</v>
+      </c>
+      <c r="D11" s="49" t="inlineStr">
+        <is>
+          <t>MARGIT RASMUSSEN</t>
+        </is>
+      </c>
+      <c r="E11" s="49" t="inlineStr">
+        <is>
+          <t>2026-039</t>
+        </is>
+      </c>
+      <c r="F11" s="49" t="inlineStr">
+        <is>
+          <t>JAN-2026</t>
+        </is>
+      </c>
+      <c r="G11" s="49" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H8" s="49" t="inlineStr">
-        <is>
-          <t>FAM-032 HOLLINGWORTH, FAM-033 IBARRA</t>
-        </is>
-      </c>
-      <c r="I8" s="49" t="inlineStr">
-        <is>
-          <t>reference 2026-024 points to FAM-033 but the memo names FAM-032  -  parent may have typed the wrong invoice number</t>
-        </is>
-      </c>
-      <c r="J8" s="49" t="inlineStr">
+      <c r="H11" s="49" t="inlineStr">
+        <is>
+          <t>FAM-048 RASMUSSEN, FAM-049 ROCHETEAU</t>
+        </is>
+      </c>
+      <c r="I11" s="49" t="inlineStr">
+        <is>
+          <t>reference 2026-039 points to FAM-049 but the memo names FAM-048  -  parent may have typed the wrong invoice number</t>
+        </is>
+      </c>
+      <c r="J11" s="49" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K8" s="48" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="B9" s="54" t="n">
-        <v>46103</v>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>434.5</v>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>YOLANDE ACHTERBERG</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Achterberg</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>JAN-2026</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>FAM-002 ACHTERBERG, FAM-003 ACHTERBERG-MARCHETTI</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>several families fit: FAM-002 (surname ACHTERBERG); FAM-003 (surname ACHTERBERG)</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K9" s="19" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="49" t="n">
-        <v>67</v>
-      </c>
-      <c r="B10" s="47" t="n">
-        <v>46133</v>
-      </c>
-      <c r="C10" s="48" t="n">
-        <v>434.5</v>
-      </c>
-      <c r="D10" s="49" t="inlineStr">
-        <is>
-          <t>MARGIT BELHADJ-TREVELYA</t>
-        </is>
-      </c>
-      <c r="E10" s="49" t="inlineStr">
-        <is>
-          <t>2026-003</t>
-        </is>
-      </c>
-      <c r="F10" s="49" t="inlineStr">
-        <is>
-          <t>JAN-2026</t>
-        </is>
-      </c>
-      <c r="G10" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H10" s="49" t="inlineStr">
-        <is>
-          <t>FAM-008 BELHADJ, FAM-009 BELHADJ-TREVELYAN, FAM-042 NAKASHIMA-PELLETIER</t>
-        </is>
-      </c>
-      <c r="I10" s="49" t="inlineStr">
-        <is>
-          <t>reference 2026-003 points to FAM-042 but the memo names FAM-008, FAM-009  -  parent may have typed the wrong invoice number</t>
-        </is>
-      </c>
-      <c r="J10" s="49" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K10" s="48" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="B11" s="54" t="n">
-        <v>46092</v>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>-409.5</v>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>REFUND</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>withdrawal refund</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>JAN-2026</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>no roster surname or child name (from the bank-sheet note, not the memo)</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K11" s="19" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="25" t="n">
-        <v>68</v>
-      </c>
-      <c r="B12" s="52" t="n">
-        <v>46133</v>
-      </c>
-      <c r="C12" s="53" t="n">
-        <v>347</v>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>TOVE CHIDOZIE</t>
-        </is>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>CHIDOZIE FRENCH SCHOO</t>
-        </is>
-      </c>
-      <c r="F12" s="25" t="inlineStr">
-        <is>
-          <t>JAN-2026</t>
-        </is>
-      </c>
-      <c r="G12" s="25" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H12" s="25" t="inlineStr">
-        <is>
-          <t>FAM-017 CHIDOZIE</t>
-        </is>
-      </c>
-      <c r="I12" s="25" t="inlineStr">
-        <is>
-          <t>surname CHIDOZIE  -  chosen over FAM-016 because only this family is billed this term</t>
-        </is>
-      </c>
-      <c r="J12" s="25" t="inlineStr">
-        <is>
-          <t>half of expected</t>
-        </is>
-      </c>
-      <c r="K12" s="53" t="n">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="25" t="n">
-        <v>80</v>
-      </c>
-      <c r="B13" s="52" t="n">
-        <v>46168</v>
-      </c>
-      <c r="C13" s="53" t="n">
-        <v>347</v>
-      </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>TOVE CHIDOZIE</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
-        <is>
-          <t>Chidozie</t>
-        </is>
-      </c>
-      <c r="F13" s="25" t="inlineStr">
-        <is>
-          <t>JAN-2026</t>
-        </is>
-      </c>
-      <c r="G13" s="25" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H13" s="25" t="inlineStr">
-        <is>
-          <t>FAM-017 CHIDOZIE</t>
-        </is>
-      </c>
-      <c r="I13" s="25" t="inlineStr">
-        <is>
-          <t>surname CHIDOZIE  -  chosen over FAM-016 because only this family is billed this term</t>
-        </is>
-      </c>
-      <c r="J13" s="25" t="inlineStr">
-        <is>
-          <t>half of expected</t>
-        </is>
-      </c>
-      <c r="K13" s="53" t="n">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" s="47" t="n">
-        <v>46038</v>
-      </c>
-      <c r="C14" s="48" t="n">
-        <v>229.75</v>
-      </c>
-      <c r="D14" s="49" t="inlineStr">
-        <is>
-          <t>MARGIT RASMUSSEN</t>
-        </is>
-      </c>
-      <c r="E14" s="49" t="inlineStr">
-        <is>
-          <t>2026-039</t>
-        </is>
-      </c>
-      <c r="F14" s="49" t="inlineStr">
-        <is>
-          <t>JAN-2026</t>
-        </is>
-      </c>
-      <c r="G14" s="49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H14" s="49" t="inlineStr">
-        <is>
-          <t>FAM-048 RASMUSSEN, FAM-049 ROCHETEAU</t>
-        </is>
-      </c>
-      <c r="I14" s="49" t="inlineStr">
-        <is>
-          <t>reference 2026-039 points to FAM-049 but the memo names FAM-048  -  parent may have typed the wrong invoice number</t>
-        </is>
-      </c>
-      <c r="J14" s="49" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K14" s="48" t="inlineStr"/>
+      <c r="K11" s="48" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K14"/>
-  <conditionalFormatting sqref="A4:K14">
+  <autoFilter ref="A3:K11"/>
+  <conditionalFormatting sqref="A4:K11">
     <cfRule type="expression" priority="1" dxfId="6">
       <formula>$G4="X"</formula>
     </cfRule>
